--- a/kuuube's_wacom_tablet_mastersheet.xlsx
+++ b/kuuube's_wacom_tablet_mastersheet.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Wacom Tablet Mastersheet" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Wacom Pen Mastersheet" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Wacom Mice Mastersheet" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Kuuubes Info" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Sources" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Wacom Tablet Mastersheet" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Wacom Pen Mastersheet" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Wacom Mice Mastersheet" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Kuuubes Info" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Sources" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -1744,220 +1744,230 @@
     </comment>
     <comment authorId="0" ref="B59">
       <text>
+        <t xml:space="preserve">(Intuos2 Designer Pen) (Design Pen)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="H59">
+      <text>
+        <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B60">
+      <text>
         <t xml:space="preserve">(Intuos2 Airbrush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H59">
+    <comment authorId="0" ref="H60">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B60">
+    <comment authorId="0" ref="B61">
       <text>
         <t xml:space="preserve">(Intuos2 Classic Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H60">
+    <comment authorId="0" ref="H61">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B61">
+    <comment authorId="0" ref="B62">
       <text>
         <t xml:space="preserve">(Intuos2 Ink Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H61">
+    <comment authorId="0" ref="H62">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B62">
+    <comment authorId="0" ref="B63">
       <text>
         <t xml:space="preserve">(Intuos2 Stroke Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H62">
+    <comment authorId="0" ref="H63">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B63">
+    <comment authorId="0" ref="B64">
       <text>
         <t xml:space="preserve">(Intuos Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H63">
+    <comment authorId="0" ref="H64">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B64">
+    <comment authorId="0" ref="B65">
       <text>
         <t xml:space="preserve">(Intuos Airbrush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H64">
+    <comment authorId="0" ref="H65">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B65">
+    <comment authorId="0" ref="B66">
       <text>
         <t xml:space="preserve">(Intuos Inking Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H65">
+    <comment authorId="0" ref="H66">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B66">
+    <comment authorId="0" ref="B67">
       <text>
         <t xml:space="preserve">(Intuos Stroke Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H66">
+    <comment authorId="0" ref="H67">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H67">
+    <comment authorId="0" ref="H68">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B68">
+    <comment authorId="0" ref="B69">
       <text>
         <t xml:space="preserve">(UltraPen Eraser) (Erasing UltraPen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H68">
+    <comment authorId="0" ref="H69">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H69">
+    <comment authorId="0" ref="H70">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B70">
+    <comment authorId="0" ref="B71">
       <text>
         <t xml:space="preserve">Click pen</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H70">
+    <comment authorId="0" ref="H71">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B71">
+    <comment authorId="0" ref="B72">
       <text>
         <t xml:space="preserve">(UltraPen Brush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H71">
+    <comment authorId="0" ref="H72">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B72">
+    <comment authorId="0" ref="B73">
       <text>
         <t xml:space="preserve">(UltraPen Pencil)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H73">
+    <comment authorId="0" ref="H74">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B74">
+    <comment authorId="0" ref="B75">
       <text>
         <t xml:space="preserve">(Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H74">
+    <comment authorId="0" ref="H75">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B75">
+    <comment authorId="0" ref="B76">
       <text>
         <t xml:space="preserve">(Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H75">
+    <comment authorId="0" ref="H76">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B76">
+    <comment authorId="0" ref="B77">
       <text>
         <t xml:space="preserve">(UltraPen 813E)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H76">
+    <comment authorId="0" ref="H77">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B77">
+    <comment authorId="0" ref="B78">
       <text>
         <t xml:space="preserve">(UltraPen Write)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H77">
+    <comment authorId="0" ref="H78">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B78">
+    <comment authorId="0" ref="B79">
       <text>
         <t xml:space="preserve">(UltraPen Write)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H78">
+    <comment authorId="0" ref="H79">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B79">
+    <comment authorId="0" ref="B80">
       <text>
         <t xml:space="preserve">(UltraPen Ink)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H79">
+    <comment authorId="0" ref="H80">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B80">
+    <comment authorId="0" ref="B81">
       <text>
         <t xml:space="preserve">(Standard Stylus Gray)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B81">
+    <comment authorId="0" ref="B82">
       <text>
         <t xml:space="preserve">(Standard Stylus Red)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B82">
+    <comment authorId="0" ref="B83">
       <text>
         <t xml:space="preserve">(Slim Stylus Gray)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B83">
+    <comment authorId="0" ref="B84">
       <text>
         <t xml:space="preserve">(Slim Stylus Magenta)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B84">
+    <comment authorId="0" ref="B85">
       <text>
         <t xml:space="preserve">(Pressure Stylus Blue)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B85">
+    <comment authorId="0" ref="B86">
       <text>
         <t xml:space="preserve">(Pressure Stylus Red)</t>
       </text>
@@ -2077,7 +2087,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="1086">
   <si>
     <t>Kuuube's Wacom Tablet Mastersheet</t>
   </si>
@@ -4189,6 +4199,12 @@
   </si>
   <si>
     <t>XD-0405-U, XD-0405-R, XD-0608-U, XD-0608-R, XD-0912-U, XD-0912-R , XD-1212-U , XD-1212-R, XD-1218-U, XD-1218-R</t>
+  </si>
+  <si>
+    <t>XP-501A</t>
+  </si>
+  <si>
+    <t>19g</t>
   </si>
   <si>
     <t>XP-400E</t>
@@ -5575,6 +5591,10 @@
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15331,30 +15351,28 @@
         <v>705</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E59" s="6">
         <v>1024.0</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>675</v>
+      <c r="F59" s="6">
+        <v>2.0</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>702</v>
+        <v>558</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="I59" s="6" t="s">
-        <v>703</v>
-      </c>
+      <c r="I59" s="6"/>
     </row>
     <row r="60">
       <c r="B60" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>707</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>603</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>708</v>
@@ -15363,7 +15381,7 @@
         <v>1024.0</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>601</v>
+        <v>675</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>702</v>
@@ -15380,22 +15398,22 @@
         <v>709</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>627</v>
+        <v>710</v>
       </c>
       <c r="E61" s="6">
         <v>1024.0</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>32</v>
+        <v>601</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>558</v>
+        <v>702</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>659</v>
+        <v>588</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>703</v>
@@ -15403,7 +15421,7 @@
     </row>
     <row r="62">
       <c r="B62" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>606</v>
@@ -15418,7 +15436,7 @@
         <v>32</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>711</v>
+        <v>558</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>659</v>
@@ -15429,45 +15447,45 @@
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>467</v>
+        <v>712</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>708</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>712</v>
+        <v>627</v>
+      </c>
+      <c r="E63" s="6">
+        <v>1024.0</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>601</v>
+        <v>32</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>588</v>
+        <v>659</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>715</v>
-      </c>
-      <c r="E64" s="6">
-        <v>1024.0</v>
-      </c>
       <c r="F64" s="6" t="s">
-        <v>675</v>
+        <v>601</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>699</v>
@@ -15476,7 +15494,7 @@
         <v>588</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="65">
@@ -15484,30 +15502,30 @@
         <v>716</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>606</v>
+        <v>707</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>627</v>
+        <v>717</v>
       </c>
       <c r="E65" s="6">
         <v>1024.0</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>32</v>
+        <v>675</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>558</v>
+        <v>699</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>659</v>
+        <v>588</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>606</v>
@@ -15522,79 +15540,79 @@
         <v>32</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>711</v>
+        <v>558</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>659</v>
       </c>
       <c r="I66" s="6" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E67" s="6">
+        <v>1024.0</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" s="6" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>719</v>
-      </c>
-      <c r="D67" s="6" t="s">
+      <c r="H67" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="6" t="s">
         <v>720</v>
       </c>
-      <c r="E67" s="6">
-        <v>256.0</v>
-      </c>
-      <c r="F67" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="I67" s="6" t="s">
+      <c r="C68" s="6" t="s">
         <v>721</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>590</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>723</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>601</v>
+      <c r="E68" s="6">
+        <v>256.0</v>
+      </c>
+      <c r="F68" s="6">
+        <v>2.0</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>635</v>
+        <v>558</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>724</v>
+        <v>281</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>590</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>722</v>
-      </c>
-      <c r="E69" s="6">
-        <v>256.0</v>
+        <v>724</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>725</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>601</v>
@@ -15606,44 +15624,44 @@
         <v>588</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>719</v>
+        <v>590</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E70" s="6">
         <v>256.0</v>
       </c>
-      <c r="F70" s="6">
-        <v>1.0</v>
+      <c r="F70" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>41</v>
+        <v>635</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>584</v>
+        <v>721</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="E71" s="6">
         <v>256.0</v>
@@ -15652,13 +15670,13 @@
         <v>1.0</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>558</v>
+        <v>41</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="72">
@@ -15669,7 +15687,7 @@
         <v>584</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E72" s="6">
         <v>256.0</v>
@@ -15681,88 +15699,88 @@
         <v>558</v>
       </c>
       <c r="H72" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>729</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="6" t="s">
-        <v>730</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>719</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>720</v>
       </c>
       <c r="E73" s="6">
         <v>256.0</v>
       </c>
       <c r="F73" s="6">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>558</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>588</v>
+        <v>731</v>
       </c>
       <c r="I73" s="6" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>669</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>732</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>733</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>601</v>
+        <v>722</v>
+      </c>
+      <c r="E74" s="6">
+        <v>256.0</v>
+      </c>
+      <c r="F74" s="6">
+        <v>2.0</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>635</v>
+        <v>558</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="D75" s="6" t="s">
+      <c r="E75" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="E75" s="6">
-        <v>512.0</v>
-      </c>
-      <c r="F75" s="6">
-        <v>2.0</v>
+      <c r="F75" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>677</v>
+        <v>635</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="76">
@@ -15773,62 +15791,62 @@
         <v>606</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>634</v>
+        <v>737</v>
       </c>
       <c r="E76" s="6">
         <v>512.0</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>601</v>
+      <c r="F76" s="6">
+        <v>2.0</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>635</v>
+        <v>677</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>719</v>
+        <v>606</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>722</v>
+        <v>634</v>
       </c>
       <c r="E77" s="6">
         <v>512.0</v>
       </c>
-      <c r="F77" s="6">
-        <v>1.0</v>
+      <c r="F77" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>558</v>
+        <v>635</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="5" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E78" s="6">
-        <v>256.0</v>
+        <v>512.0</v>
       </c>
       <c r="F78" s="6">
         <v>1.0</v>
@@ -15840,18 +15858,18 @@
         <v>588</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="5" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>584</v>
+        <v>721</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E79" s="6">
         <v>256.0</v>
@@ -15866,44 +15884,44 @@
         <v>588</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="5" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>584</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="E80" s="6">
-        <v>2.0</v>
+        <v>256.0</v>
       </c>
       <c r="F80" s="6">
         <v>1.0</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>677</v>
+        <v>558</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>742</v>
+        <v>588</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>743</v>
+        <v>723</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="5" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>584</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E81" s="6">
         <v>2.0</v>
@@ -15912,127 +15930,153 @@
         <v>1.0</v>
       </c>
       <c r="G81" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="H81" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="I81" s="6" t="s">
+    </row>
+    <row r="82">
+      <c r="B82" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="C82" s="9" t="s">
+      <c r="E82" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F82" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G82" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="D82" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>749</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>743</v>
+      <c r="H82" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="9" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>206</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="H84" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>755</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>756</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>751</v>
-      </c>
       <c r="I84" s="9" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C85" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>755</v>
-      </c>
       <c r="F85" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="C86" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="D86" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="I86" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="H85" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A36"/>
-    <mergeCell ref="A39:A85"/>
+    <mergeCell ref="A39:A86"/>
   </mergeCells>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
@@ -16058,7 +16102,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="2">
@@ -16075,13 +16119,13 @@
         <v>548</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>553</v>
@@ -16089,16 +16133,16 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>173</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E3" s="6">
         <v>3.0</v>
@@ -16107,10 +16151,10 @@
         <v>41</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="4">
@@ -16118,10 +16162,10 @@
         <v>193</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E4" s="6">
         <v>3.0</v>
@@ -16130,10 +16174,10 @@
         <v>41</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="5">
@@ -16141,10 +16185,10 @@
         <v>214</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
@@ -16153,10 +16197,10 @@
         <v>41</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6">
@@ -16164,10 +16208,10 @@
         <v>253</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E6" s="6">
         <v>3.0</v>
@@ -16176,21 +16220,21 @@
         <v>41</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="E7" s="6">
         <v>3.0</v>
@@ -16199,10 +16243,10 @@
         <v>41</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8">
@@ -16216,59 +16260,59 @@
     </row>
     <row r="9">
       <c r="B9" s="6" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E9" s="6">
         <v>5.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E10" s="6">
         <v>5.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="E11" s="6">
         <v>5.0</v>
@@ -16277,21 +16321,21 @@
         <v>587</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E12" s="6">
         <v>5.0</v>
@@ -16303,18 +16347,18 @@
         <v>32</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E13" s="6">
         <v>3.0</v>
@@ -16323,21 +16367,21 @@
         <v>655</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E14" s="6">
         <v>5.0</v>
@@ -16346,21 +16390,21 @@
         <v>587</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E15" s="6">
         <v>5.0</v>
@@ -16372,21 +16416,21 @@
         <v>32</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>587</v>
@@ -16395,18 +16439,18 @@
         <v>32</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E17" s="6">
         <v>5.0</v>
@@ -16418,7 +16462,7 @@
         <v>32</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="18">
@@ -16441,12 +16485,12 @@
         <v>41</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>41</v>
@@ -16464,7 +16508,7 @@
         <v>41</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="20">
@@ -16472,10 +16516,10 @@
         <v>519</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="E20" s="6">
         <v>4.0</v>
@@ -16487,7 +16531,7 @@
         <v>32</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="21">
@@ -16495,10 +16539,10 @@
         <v>514</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="E21" s="6">
         <v>4.0</v>
@@ -16515,13 +16559,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>574</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E22" s="6">
         <v>4.0</v>
@@ -16533,18 +16577,18 @@
         <v>32</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>816</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>814</v>
       </c>
       <c r="E23" s="6">
         <v>16.0</v>
@@ -16556,7 +16600,7 @@
         <v>32</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -16581,17 +16625,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="17" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4">
@@ -16602,57 +16646,57 @@
     </row>
     <row r="5">
       <c r="A5" s="18" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -16701,7 +16745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -16716,7 +16760,7 @@
     </row>
     <row r="2">
       <c r="A2" s="21" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -16731,1252 +16775,1252 @@
     </row>
     <row r="3">
       <c r="A3" s="24" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="24" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="25" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="25" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="25" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="25" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="25" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="25" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="25" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="25" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="25" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="25" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="25" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="25" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="25" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="25" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="25" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="25" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="25" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="25" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="25" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="25" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="25" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="25" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="25" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="25" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="25" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="25" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="25" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="25" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="25" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="25" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="25" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="25" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="25" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="25" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="25" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="25" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="25" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="25" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="25" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="25" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="25" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="25" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="25" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="25" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="25" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="25" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="25" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="25" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="25" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="25" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="25" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="25" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="25" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="25" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="25" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="25" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="25" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="25" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="25" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="25" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="25" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="25" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="25" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="25" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="25" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="25" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="25" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="25" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="25" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="25" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="25" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="25" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="25" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="25" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="25" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="25" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="25" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="25" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="25" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="25" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="25" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="25" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="25" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="25" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="25" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="25" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="25" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="25" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="25" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="25" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="25" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="25" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="25" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="25" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="25" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="25" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="25" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="25" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="25" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="25" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="25" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="25" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="25" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="25" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="25" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="25" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="25" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="25" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="25" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="25" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="25" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="25" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="25" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="25" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="25" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="25" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="25" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="25" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="25" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="25" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="25" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="25" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="25" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="25" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="25" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="25" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="25" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="25" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="25" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="25" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="25" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="25" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="25" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="25" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="25" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="25" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="25" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="25" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="25" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="25" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="25" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="25" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="25" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="25" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="25" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="25" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="25" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="25" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="25" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="25" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="25" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="25" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="25" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="25" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="25" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="25" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="25" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="25" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="25" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="25" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="25" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="25" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="25" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="25" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="25" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="25" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="25" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="25" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="25" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="25" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="25" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="25" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="25" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="25" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="25" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="25" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="25" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="25" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="25" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="25" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="25" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="25" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="25" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="25" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="25" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="25" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="25" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="25" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="25" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="25" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="25" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="25" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="25" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="25" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="25" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="25" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="25" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="25" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="25" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="25" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="25" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="25" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="25" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="25" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="25" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="25" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
   </sheetData>

--- a/kuuube's_wacom_tablet_mastersheet.xlsx
+++ b/kuuube's_wacom_tablet_mastersheet.xlsx
@@ -1577,397 +1577,407 @@
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
+    <comment authorId="0" ref="B39">
+      <text>
+        <t xml:space="preserve">(Wacom Pro Pen 3)</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="B40">
       <text>
-        <t xml:space="preserve">(Wacom Pro Pen 3)</t>
+        <t xml:space="preserve">(Wacom Pro Pen 3E)</t>
       </text>
     </comment>
     <comment authorId="0" ref="B41">
       <text>
+        <t xml:space="preserve">(Wacom Art Pen 2)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B42">
+      <text>
         <t xml:space="preserve">(Wacom Pro Pen 2)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B42">
+    <comment authorId="0" ref="B43">
       <text>
         <t xml:space="preserve">(Wacom Pro Pen Slim)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B43">
+    <comment authorId="0" ref="B44">
       <text>
         <t xml:space="preserve">(Wacom Pro Pen 3d)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B44">
+    <comment authorId="0" ref="B45">
       <text>
         <t xml:space="preserve">(Wacom Finetip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H44">
+    <comment authorId="0" ref="H45">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B45">
+    <comment authorId="0" ref="B46">
       <text>
         <t xml:space="preserve">(Wacom Ballpoint Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H45">
+    <comment authorId="0" ref="H46">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B46">
+    <comment authorId="0" ref="B47">
       <text>
         <t xml:space="preserve">(Intuos4 Grip Pen) (Intuos5 Grip Pen) (Wacom Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H46">
+    <comment authorId="0" ref="H47">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B47">
+    <comment authorId="0" ref="B48">
       <text>
         <t xml:space="preserve">(Intuos4 Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H47">
+    <comment authorId="0" ref="H48">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B48">
+    <comment authorId="0" ref="B49">
       <text>
         <t xml:space="preserve">(Wacom Pro Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H48">
+    <comment authorId="0" ref="H49">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B49">
+    <comment authorId="0" ref="B50">
       <text>
         <t xml:space="preserve">(Intuos4 Airbrush) (Intuos5 Airbrush) (Wacom Airbrush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H49">
+    <comment authorId="0" ref="H50">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B50">
+    <comment authorId="0" ref="B51">
       <text>
         <t xml:space="preserve">(Intuos4 Inking Pen) (Intuos5 Inking Pen) (Wacom Inking Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H50">
+    <comment authorId="0" ref="H51">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B51">
+    <comment authorId="0" ref="B52">
       <text>
         <t xml:space="preserve">(Intuos4 Art Pen) (Intuos5 Art Pen) (Wacom Art Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H51">
+    <comment authorId="0" ref="H52">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B52">
+    <comment authorId="0" ref="B53">
       <text>
         <t xml:space="preserve">(Intuos4 Classic Pen) (Intuos5 Classic Pen) (Wacom Classic Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H52">
+    <comment authorId="0" ref="H53">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A010-03, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A011, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B53">
+    <comment authorId="0" ref="B54">
       <text>
         <t xml:space="preserve">(Intuos3 Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H53">
+    <comment authorId="0" ref="H54">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A010-03, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A011, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B54">
+    <comment authorId="0" ref="B55">
       <text>
         <t xml:space="preserve">(Intuos3 Airbrush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H54">
+    <comment authorId="0" ref="H55">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A010-03, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A011, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B55">
+    <comment authorId="0" ref="B56">
       <text>
         <t xml:space="preserve">(Intuos3 Art Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B56">
+    <comment authorId="0" ref="B57">
       <text>
         <t xml:space="preserve">(Intuos3 Ink Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H56">
+    <comment authorId="0" ref="H57">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B57">
+    <comment authorId="0" ref="B58">
       <text>
         <t xml:space="preserve">(Intuos3 Classic Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H57">
+    <comment authorId="0" ref="H58">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B58">
+    <comment authorId="0" ref="B59">
       <text>
         <t xml:space="preserve">(Intuos2 Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H58">
+    <comment authorId="0" ref="H59">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B59">
+    <comment authorId="0" ref="B60">
       <text>
         <t xml:space="preserve">(Intuos2 Designer Pen) (Design Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H59">
+    <comment authorId="0" ref="H60">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B60">
+    <comment authorId="0" ref="B61">
       <text>
         <t xml:space="preserve">(Intuos2 Airbrush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H60">
+    <comment authorId="0" ref="H61">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B61">
+    <comment authorId="0" ref="B62">
       <text>
         <t xml:space="preserve">(Intuos2 Classic Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H61">
+    <comment authorId="0" ref="H62">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B62">
+    <comment authorId="0" ref="B63">
       <text>
         <t xml:space="preserve">(Intuos2 Ink Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H62">
+    <comment authorId="0" ref="H63">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B63">
+    <comment authorId="0" ref="B64">
       <text>
         <t xml:space="preserve">(Intuos2 Stroke Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H63">
+    <comment authorId="0" ref="H64">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B64">
+    <comment authorId="0" ref="B65">
       <text>
         <t xml:space="preserve">(Intuos Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H64">
+    <comment authorId="0" ref="H65">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B65">
+    <comment authorId="0" ref="B66">
       <text>
         <t xml:space="preserve">(Intuos Airbrush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H65">
+    <comment authorId="0" ref="H66">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B66">
+    <comment authorId="0" ref="B67">
       <text>
         <t xml:space="preserve">(Intuos Inking Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H66">
+    <comment authorId="0" ref="H67">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B67">
+    <comment authorId="0" ref="B68">
       <text>
         <t xml:space="preserve">(Intuos Stroke Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H67">
+    <comment authorId="0" ref="H68">
       <text>
         <t xml:space="preserve">(PSI-A024-BK, PSI-A025-R, PSI-A026-BL, PSI-A024-BK-01, PSI-A011, PSI-A023, FUZ-A010-03)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H68">
+    <comment authorId="0" ref="H69">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B69">
+    <comment authorId="0" ref="B70">
       <text>
         <t xml:space="preserve">(UltraPen Eraser) (Erasing UltraPen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H69">
+    <comment authorId="0" ref="H70">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H70">
+    <comment authorId="0" ref="H71">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B71">
+    <comment authorId="0" ref="B72">
       <text>
         <t xml:space="preserve">Click pen</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H71">
+    <comment authorId="0" ref="H72">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B72">
+    <comment authorId="0" ref="B73">
       <text>
         <t xml:space="preserve">(UltraPen Brush)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H72">
+    <comment authorId="0" ref="H73">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B73">
+    <comment authorId="0" ref="B74">
       <text>
         <t xml:space="preserve">(UltraPen Pencil)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H74">
+    <comment authorId="0" ref="H75">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B75">
+    <comment authorId="0" ref="B76">
       <text>
         <t xml:space="preserve">(Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H75">
+    <comment authorId="0" ref="H76">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B76">
+    <comment authorId="0" ref="B77">
       <text>
         <t xml:space="preserve">(Grip Pen)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H76">
+    <comment authorId="0" ref="H77">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B77">
+    <comment authorId="0" ref="B78">
       <text>
         <t xml:space="preserve">(UltraPen 813E)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H77">
+    <comment authorId="0" ref="H78">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B78">
+    <comment authorId="0" ref="B79">
       <text>
         <t xml:space="preserve">(UltraPen Write)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H78">
+    <comment authorId="0" ref="H79">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B79">
+    <comment authorId="0" ref="B80">
       <text>
         <t xml:space="preserve">(UltraPen Write)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H79">
+    <comment authorId="0" ref="H80">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B80">
+    <comment authorId="0" ref="B81">
       <text>
         <t xml:space="preserve">(UltraPen Ink)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H80">
+    <comment authorId="0" ref="H81">
       <text>
         <t xml:space="preserve">(ACK-20401K, ACK-20101W, ACK-20014, FUZ-A141, FUZ-A010, FUZ-A121, FUZ-A154, FUZ-A120, PSI-A034, PSI-A007, PSI-A043, PSI-A042, PSI-A066, PSI-A021)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B81">
+    <comment authorId="0" ref="B82">
       <text>
         <t xml:space="preserve">(Standard Stylus Gray)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B82">
+    <comment authorId="0" ref="B83">
       <text>
         <t xml:space="preserve">(Standard Stylus Red)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B83">
+    <comment authorId="0" ref="B84">
       <text>
         <t xml:space="preserve">(Slim Stylus Gray)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B84">
+    <comment authorId="0" ref="B85">
       <text>
         <t xml:space="preserve">(Slim Stylus Magenta)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B85">
+    <comment authorId="0" ref="B86">
       <text>
         <t xml:space="preserve">(Pressure Stylus Blue)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B86">
+    <comment authorId="0" ref="B87">
       <text>
         <t xml:space="preserve">(Pressure Stylus Red)</t>
       </text>
@@ -2087,7 +2097,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="1092">
   <si>
     <t>Kuuube's Wacom Tablet Mastersheet</t>
   </si>
@@ -3004,7 +3014,7 @@
     <t>Slight Hover Anti-chatter</t>
   </si>
   <si>
-    <t>ACP-500, ACP-501E, KP-504E, KP-301E, KP-505, KP-503E, KP-501E, KP-701E, KP-300E, KP-400E, KP-130, CP-923, CP-913, CP-202, L471-2, 180 22-1, 180J 22-1</t>
+    <t>ACP-500, ACP-501E, ACP-700, KP-504E, KP-301E, KP-505, KP-503E, KP-501E, KP-701E, KP-300E, KP-400E, KP-130, CP-923, CP-913, CP-202, L471-2, 180 22-1, 180J 22-1</t>
   </si>
   <si>
     <t>PTK-670</t>
@@ -4000,7 +4010,19 @@
     <t>KT-0405-R, KT-0608-R, UD-0608-R, UD-0608-A, UD-1212-R, UD-1212-A, UD-1218-R,UD-1218-A, KT-0405-R, KT-0405-A, KT-0405-R, KT-0405-A, UD-0608-R, UD-0608-A, UD-1212-R, UD-1212-A, UD-1218-R, UD-1825-R, CT-0405-U, CT-0405-R, CT-0405-A</t>
   </si>
   <si>
-    <t>Professional</t>
+    <t>ACP-500 [w/ weight] [w/ grip]</t>
+  </si>
+  <si>
+    <t>9.1g [12.6g] [14.4g]</t>
+  </si>
+  <si>
+    <t>160 x 8.4 mm</t>
+  </si>
+  <si>
+    <t>ACK-22211, ACK-22213, ACK-24801Z, ACK-24819Z, ACK253010Z, ACK-25611Z, ACK-256011Z, ACK-25619Z</t>
+  </si>
+  <si>
+    <t>PTK-470, PTK-670, PTK-870</t>
   </si>
   <si>
     <t>ACP-501E</t>
@@ -4009,34 +4031,37 @@
     <t>9.8g</t>
   </si>
   <si>
-    <t>160 x 8.4mm</t>
-  </si>
-  <si>
     <t>3 + Eraser</t>
   </si>
   <si>
     <t>0.1mm? (???)</t>
   </si>
   <si>
+    <t>ACP-700</t>
+  </si>
+  <si>
+    <t>15.5g</t>
+  </si>
+  <si>
+    <t>160 x 13 mm</t>
+  </si>
+  <si>
+    <t>3 + Rotation</t>
+  </si>
+  <si>
+    <t>ACK-25611Z, ACK-256011Z, ACK-25619Z</t>
+  </si>
+  <si>
+    <t>157 x 15 mm</t>
+  </si>
+  <si>
+    <t>8192 (≈&lt;1gf, &lt;1gf, 24gf, 85gf, 261gf, 794gf)</t>
+  </si>
+  <si>
+    <t>1mm? (1.5mm?)</t>
+  </si>
+  <si>
     <t>ACK-22211, ACK-22213, ACK-24801Z, ACK-24819Z, ACK253010Z</t>
-  </si>
-  <si>
-    <t>PTK-470, PTK-670, PTK-870</t>
-  </si>
-  <si>
-    <t>ACP-500 [w/ weight] [w/ grip]</t>
-  </si>
-  <si>
-    <t>9.1g [12.6g] [14.4g]</t>
-  </si>
-  <si>
-    <t>157 x 15 mm</t>
-  </si>
-  <si>
-    <t>8192 (≈&lt;1gf, &lt;1gf, 24gf, 85gf, 261gf, 794gf)</t>
-  </si>
-  <si>
-    <t>1mm? (1.5mm?)</t>
   </si>
   <si>
     <t>PTK-470, PTK-670, PTK-870, PTH-460, PTH-660, PTH-860</t>
@@ -4616,6 +4641,9 @@
   </si>
   <si>
     <t>Not all sources are directly listed. Some information may be found in links or media contained in the pages below.</t>
+  </si>
+  <si>
+    <t>https://estore.wacom.com.cn/goods_detail/901</t>
   </si>
   <si>
     <t>https://support.wacom.com/hc/ja/articles/5444635267479-Hi-uni-DIGITAL-for-Wacom%E3%81%A8Wacom-One-Pen%E3%81%AE%E9%81%95%E3%81%84%E3%81%AB%E3%81%A4%E3%81%84%E3%81%A6</t>
@@ -5817,7 +5845,7 @@
     <col customWidth="1" min="16" max="16" width="14.0"/>
     <col customWidth="1" min="17" max="17" width="67.0"/>
     <col customWidth="1" min="18" max="18" width="37.29"/>
-    <col customWidth="1" min="19" max="19" width="135.29"/>
+    <col customWidth="1" min="19" max="19" width="145.43"/>
     <col customWidth="1" min="20" max="20" width="21.0"/>
   </cols>
   <sheetData>
@@ -13857,7 +13885,7 @@
     <col customWidth="1" min="5" max="5" width="91.57"/>
     <col customWidth="1" min="6" max="6" width="18.71"/>
     <col customWidth="1" min="7" max="7" width="26.57"/>
-    <col customWidth="1" min="8" max="8" width="79.86"/>
+    <col customWidth="1" min="8" max="8" width="93.0"/>
     <col customWidth="1" min="9" max="9" width="211.14"/>
   </cols>
   <sheetData>
@@ -14821,162 +14849,160 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>639</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>640</v>
       </c>
       <c r="E39" s="6">
         <v>8192.0</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>641</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E40" s="6">
         <v>8192.0</v>
       </c>
-      <c r="F40" s="6">
-        <v>3.0</v>
+      <c r="F40" s="6" t="s">
+        <v>644</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>558</v>
+        <v>645</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>325</v>
+        <v>646</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>569</v>
+        <v>647</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="E41" s="6" t="s">
         <v>648</v>
       </c>
+      <c r="E41" s="6">
+        <v>8192.0</v>
+      </c>
       <c r="F41" s="6" t="s">
-        <v>601</v>
+        <v>649</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>649</v>
+        <v>41</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="I41" s="6" t="s">
         <v>650</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>651</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="D42" s="6" t="s">
+      <c r="E42" s="6" t="s">
         <v>652</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>653</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>601</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="E43" s="6">
-        <v>8192.0</v>
-      </c>
-      <c r="F43" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="G43" s="6" t="s">
+      <c r="I43" s="6" t="s">
         <v>655</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>657</v>
+        <v>569</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E44" s="6">
         <v>8192.0</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>32</v>
+      <c r="F44" s="6">
+        <v>3.0</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>655</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="45">
@@ -14984,10 +15010,10 @@
         <v>661</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="E45" s="6">
         <v>8192.0</v>
@@ -14996,18 +15022,18 @@
         <v>32</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="5" t="s">
-        <v>346</v>
+        <v>666</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>662</v>
@@ -15015,20 +15041,20 @@
       <c r="D46" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="6">
+        <v>8192.0</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="H46" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="I46" s="6" t="s">
         <v>665</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="47">
@@ -15036,233 +15062,233 @@
         <v>346</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>601</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>669</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>671</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>601</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>649</v>
+        <v>672</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>674</v>
-      </c>
-      <c r="E49" s="6">
-        <v>2048.0</v>
+        <v>675</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>676</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>675</v>
+        <v>601</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>606</v>
+        <v>678</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>627</v>
+        <v>679</v>
       </c>
       <c r="E50" s="6">
         <v>2048.0</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>32</v>
+        <v>680</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>659</v>
+        <v>588</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>679</v>
+        <v>606</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>680</v>
+        <v>627</v>
       </c>
       <c r="E51" s="6">
         <v>2048.0</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>681</v>
+        <v>32</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>588</v>
+        <v>664</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>606</v>
+        <v>684</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E52" s="6">
         <v>2048.0</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>601</v>
+        <v>686</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>684</v>
+        <v>588</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>396</v>
+        <v>687</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>662</v>
+        <v>606</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>686</v>
+        <v>688</v>
+      </c>
+      <c r="E53" s="6">
+        <v>2048.0</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>601</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="5" t="s">
-        <v>689</v>
+        <v>396</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>674</v>
-      </c>
-      <c r="E54" s="6">
-        <v>1024.0</v>
+      <c r="E54" s="6" t="s">
+        <v>691</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>601</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>608</v>
+        <v>695</v>
       </c>
       <c r="D55" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="E55" s="6">
+        <v>1024.0</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G55" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="H55" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="I55" s="6" t="s">
         <v>693</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>694</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>677</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>695</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="56">
@@ -15270,184 +15296,184 @@
         <v>696</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="E56" s="6">
-        <v>1024.0</v>
+      <c r="E56" s="6" t="s">
+        <v>698</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>32</v>
+        <v>699</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>659</v>
+        <v>700</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>606</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="E57" s="6">
         <v>1024.0</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>601</v>
+        <v>32</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>588</v>
+        <v>664</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="5" t="s">
-        <v>436</v>
+        <v>703</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>662</v>
+        <v>606</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>700</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>701</v>
+        <v>688</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1024.0</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>601</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>704</v>
+        <v>436</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>705</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>700</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1024.0</v>
-      </c>
-      <c r="F59" s="6">
-        <v>2.0</v>
+      <c r="E59" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>558</v>
+        <v>707</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="I59" s="6"/>
+      <c r="I59" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E60" s="6">
         <v>1024.0</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>675</v>
+      <c r="F60" s="6">
+        <v>2.0</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>702</v>
+        <v>558</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="I60" s="6" t="s">
-        <v>703</v>
-      </c>
+      <c r="I60" s="6"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>603</v>
+        <v>712</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E61" s="6">
         <v>1024.0</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>601</v>
+        <v>680</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>627</v>
+        <v>715</v>
       </c>
       <c r="E62" s="6">
         <v>1024.0</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>32</v>
+        <v>601</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>558</v>
+        <v>707</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>659</v>
+        <v>588</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>606</v>
@@ -15462,96 +15488,96 @@
         <v>32</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>713</v>
+        <v>558</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="5" t="s">
-        <v>467</v>
+        <v>717</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>710</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>714</v>
+        <v>627</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1024.0</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>601</v>
+        <v>32</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>699</v>
+        <v>718</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>588</v>
+        <v>664</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>716</v>
+        <v>467</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>707</v>
+        <v>603</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>717</v>
-      </c>
-      <c r="E65" s="6">
-        <v>1024.0</v>
+        <v>715</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>719</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>675</v>
+        <v>601</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>606</v>
+        <v>712</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>627</v>
+        <v>722</v>
       </c>
       <c r="E66" s="6">
         <v>1024.0</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>32</v>
+        <v>680</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>558</v>
+        <v>704</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>659</v>
+        <v>588</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>606</v>
@@ -15566,79 +15592,79 @@
         <v>32</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>713</v>
+        <v>558</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E68" s="6">
+        <v>1024.0</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="I68" s="6" t="s">
         <v>720</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>721</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>722</v>
-      </c>
-      <c r="E68" s="6">
+    </row>
+    <row r="69">
+      <c r="B69" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="E69" s="6">
         <v>256.0</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F69" s="6">
         <v>2.0</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G69" s="6" t="s">
         <v>558</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>724</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>725</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>635</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="5" t="s">
-        <v>726</v>
+        <v>281</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>590</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>724</v>
-      </c>
-      <c r="E70" s="6">
-        <v>256.0</v>
+        <v>729</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>730</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>601</v>
@@ -15650,44 +15676,44 @@
         <v>588</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>721</v>
+        <v>590</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E71" s="6">
         <v>256.0</v>
       </c>
-      <c r="F71" s="6">
-        <v>1.0</v>
+      <c r="F71" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>41</v>
+        <v>635</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>584</v>
+        <v>726</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E72" s="6">
         <v>256.0</v>
@@ -15696,24 +15722,24 @@
         <v>1.0</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>558</v>
+        <v>41</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>584</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="E73" s="6">
         <v>256.0</v>
@@ -15725,154 +15751,154 @@
         <v>558</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>731</v>
+        <v>588</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="6" t="s">
-        <v>732</v>
+      <c r="B74" s="5" t="s">
+        <v>735</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>721</v>
+        <v>584</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="E74" s="6">
         <v>256.0</v>
       </c>
       <c r="F74" s="6">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>558</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>588</v>
+        <v>736</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="5" t="s">
-        <v>733</v>
+      <c r="B75" s="6" t="s">
+        <v>737</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>669</v>
+        <v>726</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>734</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>601</v>
+        <v>727</v>
+      </c>
+      <c r="E75" s="6">
+        <v>256.0</v>
+      </c>
+      <c r="F75" s="6">
+        <v>2.0</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>635</v>
+        <v>558</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="5" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>606</v>
+        <v>674</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>737</v>
-      </c>
-      <c r="E76" s="6">
-        <v>512.0</v>
-      </c>
-      <c r="F76" s="6">
-        <v>2.0</v>
+        <v>739</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>677</v>
+        <v>635</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>606</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>634</v>
+        <v>742</v>
       </c>
       <c r="E77" s="6">
         <v>512.0</v>
       </c>
-      <c r="F77" s="6" t="s">
-        <v>601</v>
+      <c r="F77" s="6">
+        <v>2.0</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>721</v>
+        <v>606</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>724</v>
+        <v>634</v>
       </c>
       <c r="E78" s="6">
         <v>512.0</v>
       </c>
-      <c r="F78" s="6">
-        <v>1.0</v>
+      <c r="F78" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>558</v>
+        <v>635</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>588</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="E79" s="6">
-        <v>256.0</v>
+        <v>512.0</v>
       </c>
       <c r="F79" s="6">
         <v>1.0</v>
@@ -15884,15 +15910,15 @@
         <v>588</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="5" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>584</v>
+        <v>726</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>729</v>
@@ -15910,44 +15936,44 @@
         <v>588</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>584</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="E81" s="6">
-        <v>2.0</v>
+        <v>256.0</v>
       </c>
       <c r="F81" s="6">
         <v>1.0</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>677</v>
+        <v>558</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>744</v>
+        <v>588</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="5" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>584</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E82" s="6">
         <v>2.0</v>
@@ -15956,127 +15982,153 @@
         <v>1.0</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>747</v>
+        <v>682</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="E83" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F83" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="H83" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="I83" s="6" t="s">
         <v>750</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>751</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>749</v>
-      </c>
       <c r="D84" s="9" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>206</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="D85" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="E85" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F85" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="E85" s="10" t="s">
+      <c r="G85" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="H85" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="G85" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>753</v>
-      </c>
       <c r="I85" s="9" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="9" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="F86" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="H86" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>753</v>
-      </c>
       <c r="I86" s="9" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4"/>
+      <c r="B87" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A36"/>
-    <mergeCell ref="A39:A86"/>
+    <mergeCell ref="A39:A87"/>
   </mergeCells>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
@@ -16102,7 +16154,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="2">
@@ -16119,13 +16171,13 @@
         <v>548</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>553</v>
@@ -16133,16 +16185,16 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>173</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="E3" s="6">
         <v>3.0</v>
@@ -16151,10 +16203,10 @@
         <v>41</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4">
@@ -16162,10 +16214,10 @@
         <v>193</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="E4" s="6">
         <v>3.0</v>
@@ -16174,10 +16226,10 @@
         <v>41</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="5">
@@ -16185,10 +16237,10 @@
         <v>214</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
@@ -16197,10 +16249,10 @@
         <v>41</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6">
@@ -16208,10 +16260,10 @@
         <v>253</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="E6" s="6">
         <v>3.0</v>
@@ -16220,21 +16272,21 @@
         <v>41</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="E7" s="6">
         <v>3.0</v>
@@ -16243,10 +16295,10 @@
         <v>41</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8">
@@ -16260,59 +16312,59 @@
     </row>
     <row r="9">
       <c r="B9" s="6" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="E9" s="6">
         <v>5.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E10" s="6">
         <v>5.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="E11" s="6">
         <v>5.0</v>
@@ -16321,21 +16373,21 @@
         <v>587</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="E12" s="6">
         <v>5.0</v>
@@ -16347,41 +16399,41 @@
         <v>32</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E13" s="6">
         <v>3.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="E14" s="6">
         <v>5.0</v>
@@ -16390,21 +16442,21 @@
         <v>587</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="E15" s="6">
         <v>5.0</v>
@@ -16416,21 +16468,21 @@
         <v>32</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>587</v>
@@ -16439,18 +16491,18 @@
         <v>32</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="E17" s="6">
         <v>5.0</v>
@@ -16462,7 +16514,7 @@
         <v>32</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
     <row r="18">
@@ -16485,12 +16537,12 @@
         <v>41</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>41</v>
@@ -16508,7 +16560,7 @@
         <v>41</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
     </row>
     <row r="20">
@@ -16516,10 +16568,10 @@
         <v>519</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="E20" s="6">
         <v>4.0</v>
@@ -16531,7 +16583,7 @@
         <v>32</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
     </row>
     <row r="21">
@@ -16539,10 +16591,10 @@
         <v>514</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="E21" s="6">
         <v>4.0</v>
@@ -16559,13 +16611,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>574</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="E22" s="6">
         <v>4.0</v>
@@ -16577,18 +16629,18 @@
         <v>32</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="E23" s="6">
         <v>16.0</v>
@@ -16600,7 +16652,7 @@
         <v>32</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -16625,17 +16677,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="17" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4">
@@ -16646,57 +16698,57 @@
     </row>
     <row r="5">
       <c r="A5" s="18" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -16708,7 +16760,7 @@
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A15:K15"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -16745,7 +16797,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -16760,7 +16812,7 @@
     </row>
     <row r="2">
       <c r="A2" s="21" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -16775,1252 +16827,1257 @@
     </row>
     <row r="3">
       <c r="A3" s="24" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="24" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="s">
-        <v>838</v>
+      <c r="A5" s="24" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="25" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="25" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="25" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="25" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="25" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="25" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="25" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="25" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="25" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="25" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="25" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="25" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="25" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="25" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="25" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="25" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="25" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="25" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="25" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="25" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="25" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="25" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="25" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="25" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="25" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="25" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="25" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="25" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="25" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="25" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="25" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="25" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="25" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="25" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="25" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="25" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="25" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="25" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="25" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="25" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="25" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="25" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="25" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="25" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="25" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="25" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="25" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="25" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="25" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="25" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="25" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="25" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="25" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="25" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="25" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="25" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="25" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="25" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="25" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="25" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="25" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="25" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="25" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="25" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="25" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="25" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="25" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="25" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="25" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="25" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="25" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="25" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="25" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="25" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="25" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="25" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="25" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="25" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="25" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="25" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="25" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="25" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="25" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="25" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="25" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="25" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="25" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="25" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="25" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="25" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="25" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="25" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="25" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="25" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="25" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="25" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="25" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="25" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="25" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="25" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="25" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="25" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="25" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="25" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="25" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="25" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="25" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="25" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="25" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="25" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="25" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="25" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="25" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="25" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="25" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="25" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="25" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="25" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="25" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="25" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="25" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="25" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="25" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="25" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="25" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="25" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="25" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="25" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="25" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="25" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="25" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="25" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="25" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="25" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="25" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="25" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="25" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="25" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="25" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="25" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="25" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="25" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="25" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="25" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="25" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="25" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="25" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="25" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="25" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="25" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="25" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="25" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="25" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="25" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="25" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="25" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="25" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="25" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="25" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="25" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="25" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="25" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="25" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="25" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="25" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="25" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="25" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="25" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="25" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="25" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="25" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="25" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="25" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="25" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="25" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="25" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="25" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="25" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="25" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="25" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="25" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="25" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="25" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="25" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="25" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="25" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="25" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="25" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="25" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="25" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="25" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="25" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="25" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="25" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="25" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="25" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="25" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="25" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="25" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="25" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="25" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="25" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="25" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="25" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="25" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="25" t="s">
-        <v>1085</v>
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="25" t="s">
+        <v>1091</v>
       </c>
     </row>
   </sheetData>
@@ -18275,7 +18332,8 @@
     <hyperlink r:id="rId248" ref="A250"/>
     <hyperlink r:id="rId249" ref="A251"/>
     <hyperlink r:id="rId250" ref="A252"/>
+    <hyperlink r:id="rId251" ref="A253"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId252"/>
 </worksheet>
 </file>